--- a/output/topology_excel/3844.xlsx
+++ b/output/topology_excel/3844.xlsx
@@ -425,58 +425,38 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>房间1</t>
+          <t>RoomA</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>类型1</t>
+          <t>RoomB</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>面积1</t>
+          <t>ConnectionType</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>房间2</t>
+          <t>Count</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>类型2</t>
+          <t>Length</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>面积2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>连接类型</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>数量</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>length</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>width</t>
+          <t>Width</t>
         </is>
       </c>
     </row>
@@ -484,37 +464,21 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
-      </c>
-      <c r="C2" t="n">
-        <v>247724</v>
+      <c r="B2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D2" t="n">
-        <v>2</v>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E2" t="n">
+        <v>82</v>
       </c>
       <c r="F2" t="n">
-        <v>135132</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1</v>
-      </c>
-      <c r="I2" t="n">
-        <v>82</v>
-      </c>
-      <c r="J2" t="n">
         <v>14</v>
       </c>
     </row>
@@ -522,37 +486,21 @@
       <c r="A3" t="n">
         <v>1</v>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>247724</v>
+      <c r="B3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E3" t="n">
+        <v>64</v>
       </c>
       <c r="F3" t="n">
-        <v>29223</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>1</v>
-      </c>
-      <c r="I3" t="n">
-        <v>64</v>
-      </c>
-      <c r="J3" t="n">
         <v>15</v>
       </c>
     </row>
@@ -560,37 +508,21 @@
       <c r="A4" t="n">
         <v>2</v>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>135132</v>
+      <c r="B4" t="n">
+        <v>4</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D4" t="n">
-        <v>4</v>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>73</v>
       </c>
       <c r="F4" t="n">
-        <v>131946</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H4" t="n">
-        <v>1</v>
-      </c>
-      <c r="I4" t="n">
-        <v>73</v>
-      </c>
-      <c r="J4" t="n">
         <v>20</v>
       </c>
     </row>
@@ -598,37 +530,21 @@
       <c r="A5" t="n">
         <v>1</v>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>247724</v>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Door</t>
+        </is>
       </c>
       <c r="D5" t="n">
-        <v>4</v>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E5" t="n">
+        <v>87</v>
       </c>
       <c r="F5" t="n">
-        <v>131946</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>门</t>
-        </is>
-      </c>
-      <c r="H5" t="n">
-        <v>1</v>
-      </c>
-      <c r="I5" t="n">
-        <v>87</v>
-      </c>
-      <c r="J5" t="n">
         <v>15</v>
       </c>
     </row>
@@ -636,37 +552,21 @@
       <c r="A6" t="n">
         <v>1</v>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>247724</v>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Window</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E6" t="n">
+        <v>225</v>
       </c>
       <c r="F6" t="n">
-        <v>135132</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>窗</t>
-        </is>
-      </c>
-      <c r="H6" t="n">
-        <v>1</v>
-      </c>
-      <c r="I6" t="n">
-        <v>225</v>
-      </c>
-      <c r="J6" t="n">
         <v>14</v>
       </c>
     </row>
@@ -674,37 +574,21 @@
       <c r="A7" t="n">
         <v>1</v>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>247724</v>
+      <c r="B7" t="n">
+        <v>2</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E7" t="n">
+        <v>243</v>
       </c>
       <c r="F7" t="n">
-        <v>135132</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H7" t="n">
-        <v>1</v>
-      </c>
-      <c r="I7" t="n">
-        <v>243</v>
-      </c>
-      <c r="J7" t="n">
         <v>118</v>
       </c>
     </row>
@@ -712,37 +596,21 @@
       <c r="A8" t="n">
         <v>1</v>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>247724</v>
+      <c r="B8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>3</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E8" t="n">
+        <v>153</v>
       </c>
       <c r="F8" t="n">
-        <v>29223</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H8" t="n">
-        <v>1</v>
-      </c>
-      <c r="I8" t="n">
-        <v>153</v>
-      </c>
-      <c r="J8" t="n">
         <v>15</v>
       </c>
     </row>
@@ -750,37 +618,21 @@
       <c r="A9" t="n">
         <v>1</v>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Living Room</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>247724</v>
+      <c r="B9" t="n">
+        <v>4</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>4</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E9" t="n">
+        <v>161</v>
       </c>
       <c r="F9" t="n">
-        <v>131946</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H9" t="n">
-        <v>1</v>
-      </c>
-      <c r="I9" t="n">
-        <v>161</v>
-      </c>
-      <c r="J9" t="n">
         <v>15</v>
       </c>
     </row>
@@ -788,37 +640,21 @@
       <c r="A10" t="n">
         <v>2</v>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>135132</v>
+      <c r="B10" t="n">
+        <v>3</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>3</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E10" t="n">
+        <v>229</v>
       </c>
       <c r="F10" t="n">
-        <v>29223</v>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H10" t="n">
-        <v>1</v>
-      </c>
-      <c r="I10" t="n">
-        <v>229</v>
-      </c>
-      <c r="J10" t="n">
         <v>167</v>
       </c>
     </row>
@@ -826,37 +662,21 @@
       <c r="A11" t="n">
         <v>2</v>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>135132</v>
+      <c r="B11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D11" t="n">
-        <v>4</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E11" t="n">
+        <v>147</v>
       </c>
       <c r="F11" t="n">
-        <v>131946</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H11" t="n">
-        <v>1</v>
-      </c>
-      <c r="I11" t="n">
-        <v>147</v>
-      </c>
-      <c r="J11" t="n">
         <v>20</v>
       </c>
     </row>
@@ -864,37 +684,21 @@
       <c r="A12" t="n">
         <v>3</v>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Bath</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>29223</v>
+      <c r="B12" t="n">
+        <v>4</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
       </c>
       <c r="D12" t="n">
-        <v>4</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Bedroom</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>191</v>
       </c>
       <c r="F12" t="n">
-        <v>131946</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>墙</t>
-        </is>
-      </c>
-      <c r="H12" t="n">
-        <v>1</v>
-      </c>
-      <c r="I12" t="n">
-        <v>191</v>
-      </c>
-      <c r="J12" t="n">
         <v>20</v>
       </c>
     </row>

--- a/output/topology_excel/3844.xlsx
+++ b/output/topology_excel/3844.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F12"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,10 +462,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -484,10 +484,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -506,7 +506,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" t="n">
         <v>4</v>
@@ -528,10 +528,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -550,10 +550,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -575,7 +575,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -586,10 +586,10 @@
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>243</v>
+        <v>66</v>
       </c>
       <c r="F7" t="n">
-        <v>118</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -597,7 +597,7 @@
         <v>1</v>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -608,10 +608,10 @@
         <v>1</v>
       </c>
       <c r="E8" t="n">
-        <v>153</v>
+        <v>167</v>
       </c>
       <c r="F8" t="n">
-        <v>15</v>
+        <v>137</v>
       </c>
     </row>
     <row r="9">
@@ -630,10 +630,10 @@
         <v>1</v>
       </c>
       <c r="E9" t="n">
-        <v>161</v>
+        <v>147</v>
       </c>
       <c r="F9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -655,15 +655,15 @@
         <v>229</v>
       </c>
       <c r="F10" t="n">
-        <v>167</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B11" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -674,10 +674,10 @@
         <v>1</v>
       </c>
       <c r="E11" t="n">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="F11" t="n">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="12">
@@ -685,21 +685,395 @@
         <v>3</v>
       </c>
       <c r="B12" t="n">
+        <v>5</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>1</v>
+      </c>
+      <c r="E12" t="n">
+        <v>92</v>
+      </c>
+      <c r="F12" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
         <v>4</v>
       </c>
-      <c r="C12" t="inlineStr">
+      <c r="B13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>Wall</t>
         </is>
       </c>
-      <c r="D12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="D13" t="n">
+        <v>1</v>
+      </c>
+      <c r="E13" t="n">
         <v>191</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F13" t="n">
         <v>20</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B14" t="n">
+        <v>6</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" t="n">
+        <v>161</v>
+      </c>
+      <c r="F14" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>5</v>
+      </c>
+      <c r="B15" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Wall</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" t="n">
+        <v>153</v>
+      </c>
+      <c r="F15" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>1</v>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>1</v>
+      </c>
+      <c r="E16" t="n">
+        <v>163</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>1</v>
+      </c>
+      <c r="E17" t="n">
+        <v>12</v>
+      </c>
+      <c r="F17" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2</v>
+      </c>
+      <c r="B18" t="n">
+        <v>6</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>1</v>
+      </c>
+      <c r="E18" t="n">
+        <v>12</v>
+      </c>
+      <c r="F18" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2</v>
+      </c>
+      <c r="B19" t="n">
+        <v>6</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>1</v>
+      </c>
+      <c r="E19" t="n">
+        <v>12</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2</v>
+      </c>
+      <c r="B20" t="n">
+        <v>6</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E20" t="n">
+        <v>12</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2</v>
+      </c>
+      <c r="B21" t="n">
+        <v>6</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>1</v>
+      </c>
+      <c r="E21" t="n">
+        <v>12</v>
+      </c>
+      <c r="F21" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" t="n">
+        <v>6</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="n">
+        <v>12</v>
+      </c>
+      <c r="F22" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2</v>
+      </c>
+      <c r="B23" t="n">
+        <v>6</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>1</v>
+      </c>
+      <c r="E23" t="n">
+        <v>12</v>
+      </c>
+      <c r="F23" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B24" t="n">
+        <v>6</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>1</v>
+      </c>
+      <c r="E24" t="n">
+        <v>12</v>
+      </c>
+      <c r="F24" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2</v>
+      </c>
+      <c r="B25" t="n">
+        <v>6</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
+      </c>
+      <c r="E25" t="n">
+        <v>12</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2</v>
+      </c>
+      <c r="B26" t="n">
+        <v>6</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E26" t="n">
+        <v>12</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2</v>
+      </c>
+      <c r="B27" t="n">
+        <v>6</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>1</v>
+      </c>
+      <c r="E27" t="n">
+        <v>12</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2</v>
+      </c>
+      <c r="B28" t="n">
+        <v>6</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>1</v>
+      </c>
+      <c r="E28" t="n">
+        <v>12</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2</v>
+      </c>
+      <c r="B29" t="n">
+        <v>6</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Opening</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
+      </c>
+      <c r="E29" t="n">
+        <v>11</v>
+      </c>
+      <c r="F29" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/topology_excel/3844.xlsx
+++ b/output/topology_excel/3844.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F29"/>
+  <dimension ref="A1:AD17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,12 +451,132 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Length</t>
+          <t>Length_1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>Width</t>
+          <t>Width_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Length_2</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Width_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Length_3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Width_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Length_4</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Width_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Length_5</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Width_5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Length_6</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Width_6</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Length_7</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Width_7</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Length_8</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Width_8</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Length_9</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>Width_9</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Length_10</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Width_10</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Length_11</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>Width_11</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>Length_12</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>Width_12</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>Length_13</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>Width_13</t>
         </is>
       </c>
     </row>
@@ -481,6 +601,30 @@
       <c r="F2" t="n">
         <v>14</v>
       </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -503,6 +647,30 @@
       <c r="F3" t="n">
         <v>15</v>
       </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -525,6 +693,30 @@
       <c r="F4" t="n">
         <v>20</v>
       </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -547,6 +739,30 @@
       <c r="F5" t="n">
         <v>15</v>
       </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -569,6 +785,30 @@
       <c r="F6" t="n">
         <v>14</v>
       </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -591,6 +831,30 @@
       <c r="F7" t="n">
         <v>42</v>
       </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -605,14 +869,42 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
-        <v>167</v>
+        <v>99</v>
       </c>
       <c r="F8" t="n">
-        <v>137</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="G8" t="n">
+        <v>153</v>
+      </c>
+      <c r="H8" t="n">
+        <v>38</v>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -635,6 +927,30 @@
       <c r="F9" t="n">
         <v>20</v>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -657,6 +973,30 @@
       <c r="F10" t="n">
         <v>14</v>
       </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -679,6 +1019,30 @@
       <c r="F11" t="n">
         <v>14</v>
       </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -701,6 +1065,30 @@
       <c r="F12" t="n">
         <v>14</v>
       </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -723,6 +1111,30 @@
       <c r="F13" t="n">
         <v>20</v>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -745,6 +1157,30 @@
       <c r="F14" t="n">
         <v>15</v>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -767,6 +1203,30 @@
       <c r="F15" t="n">
         <v>15</v>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -789,6 +1249,30 @@
       <c r="F16" t="n">
         <v>1</v>
       </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -803,7 +1287,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="E17" t="n">
         <v>12</v>
@@ -811,268 +1295,76 @@
       <c r="F17" t="n">
         <v>1</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>2</v>
-      </c>
-      <c r="B18" t="n">
-        <v>6</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" t="n">
+      <c r="G17" t="n">
         <v>12</v>
       </c>
-      <c r="F18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>2</v>
-      </c>
-      <c r="B19" t="n">
-        <v>6</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>1</v>
-      </c>
-      <c r="E19" t="n">
+      <c r="H17" t="n">
+        <v>1</v>
+      </c>
+      <c r="I17" t="n">
         <v>12</v>
       </c>
-      <c r="F19" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>2</v>
-      </c>
-      <c r="B20" t="n">
-        <v>6</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>1</v>
-      </c>
-      <c r="E20" t="n">
+      <c r="J17" t="n">
+        <v>1</v>
+      </c>
+      <c r="K17" t="n">
         <v>12</v>
       </c>
-      <c r="F20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>2</v>
-      </c>
-      <c r="B21" t="n">
-        <v>6</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>1</v>
-      </c>
-      <c r="E21" t="n">
+      <c r="L17" t="n">
+        <v>1</v>
+      </c>
+      <c r="M17" t="n">
         <v>12</v>
       </c>
-      <c r="F21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>2</v>
-      </c>
-      <c r="B22" t="n">
-        <v>6</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>1</v>
-      </c>
-      <c r="E22" t="n">
+      <c r="N17" t="n">
+        <v>1</v>
+      </c>
+      <c r="O17" t="n">
         <v>12</v>
       </c>
-      <c r="F22" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2</v>
-      </c>
-      <c r="B23" t="n">
-        <v>6</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>1</v>
-      </c>
-      <c r="E23" t="n">
+      <c r="P17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q17" t="n">
         <v>12</v>
       </c>
-      <c r="F23" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>2</v>
-      </c>
-      <c r="B24" t="n">
-        <v>6</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>1</v>
-      </c>
-      <c r="E24" t="n">
+      <c r="R17" t="n">
+        <v>1</v>
+      </c>
+      <c r="S17" t="n">
         <v>12</v>
       </c>
-      <c r="F24" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>2</v>
-      </c>
-      <c r="B25" t="n">
-        <v>6</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>1</v>
-      </c>
-      <c r="E25" t="n">
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
         <v>12</v>
       </c>
-      <c r="F25" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>2</v>
-      </c>
-      <c r="B26" t="n">
-        <v>6</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>1</v>
-      </c>
-      <c r="E26" t="n">
+      <c r="V17" t="n">
+        <v>1</v>
+      </c>
+      <c r="W17" t="n">
         <v>12</v>
       </c>
-      <c r="F26" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>2</v>
-      </c>
-      <c r="B27" t="n">
-        <v>6</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>1</v>
-      </c>
-      <c r="E27" t="n">
+      <c r="X17" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y17" t="n">
         <v>12</v>
       </c>
-      <c r="F27" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>2</v>
-      </c>
-      <c r="B28" t="n">
-        <v>6</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>1</v>
-      </c>
-      <c r="E28" t="n">
+      <c r="Z17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA17" t="n">
         <v>12</v>
       </c>
-      <c r="F28" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>2</v>
-      </c>
-      <c r="B29" t="n">
-        <v>6</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Opening</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>1</v>
-      </c>
-      <c r="E29" t="n">
+      <c r="AB17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AC17" t="n">
         <v>11</v>
       </c>
-      <c r="F29" t="n">
+      <c r="AD17" t="n">
         <v>1</v>
       </c>
     </row>
